--- a/public/assets/plantilla/import.xlsx
+++ b/public/assets/plantilla/import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luis.castanedal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2CD170-21A6-4BBB-A0C7-93972B525286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2136D463-A660-4C3B-8763-C0ED0BE3C551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B2A7F7DE-CD23-4E5D-90CB-B1B724898F83}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B2A7F7DE-CD23-4E5D-90CB-B1B724898F83}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -153,12 +153,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -173,8 +179,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,10 +531,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" t="s">
@@ -30633,14 +30640,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="57f08f8d-a9a1-4fdd-bb65-b5a1b4fbd46d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010034882FCD6D29CF49BF73FAA9378D216A" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8bec588dc91a0069c61fedb46d8c8cc2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="57f08f8d-a9a1-4fdd-bb65-b5a1b4fbd46d" xmlns:ns4="81430790-04b2-409f-b11e-ef1b6d161e8d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eea2de9b33a59d26ec5df18787a90c6f" ns3:_="" ns4:_="">
     <xsd:import namespace="57f08f8d-a9a1-4fdd-bb65-b5a1b4fbd46d"/>
@@ -30879,6 +30878,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="57f08f8d-a9a1-4fdd-bb65-b5a1b4fbd46d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -30889,23 +30896,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BE15FB-5298-4BD7-9B65-74848560E736}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="81430790-04b2-409f-b11e-ef1b6d161e8d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="57f08f8d-a9a1-4fdd-bb65-b5a1b4fbd46d"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49EBFBA0-3B75-4756-9C8F-4E548F5DB475}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30924,6 +30914,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BE15FB-5298-4BD7-9B65-74848560E736}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="81430790-04b2-409f-b11e-ef1b6d161e8d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="57f08f8d-a9a1-4fdd-bb65-b5a1b4fbd46d"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{201F5D79-C243-457B-9572-CF29FED304A6}">
   <ds:schemaRefs>
